--- a/artfynd/A 41689-2024 artfynd.xlsx
+++ b/artfynd/A 41689-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,127 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123301046</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ålhustjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>615932</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6973960</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 41689-2024 artfynd.xlsx
+++ b/artfynd/A 41689-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301046</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41689-2024 artfynd.xlsx
+++ b/artfynd/A 41689-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301046</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41689-2024 artfynd.xlsx
+++ b/artfynd/A 41689-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301046</v>
       </c>
       <c r="B3" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41689-2024 artfynd.xlsx
+++ b/artfynd/A 41689-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301046</v>
       </c>
       <c r="B3" t="n">
-        <v>79853</v>
+        <v>79856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41689-2024 artfynd.xlsx
+++ b/artfynd/A 41689-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301046</v>
       </c>
       <c r="B3" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41689-2024 artfynd.xlsx
+++ b/artfynd/A 41689-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301046</v>
       </c>
       <c r="B3" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41689-2024 artfynd.xlsx
+++ b/artfynd/A 41689-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301046</v>
       </c>
       <c r="B3" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
